--- a/SuppXLS/Scen_B_IND_Shares.xlsx
+++ b/SuppXLS/Scen_B_IND_Shares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF\tim-leaf v1.3BS\tim-leaf v1.3BS\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A45167F-001C-4415-BA4B-2202657041E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756B959F-B6C2-4AC2-AAEE-5DD4832640A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IND" sheetId="2" r:id="rId1"/>
@@ -2788,7 +2788,8 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" customWidth="1"/>
+    <col min="10" max="10" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:11">
